--- a/extenbooks/S501_extenbook.xlsx
+++ b/extenbooks/S501_extenbook.xlsx
@@ -9347,7 +9347,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>**Status**: ingested · **Authored**: 2026-05-18 · **Author**: opus-fanout-wave3-ch5</t>
+          <t>**Status**: book_period_validated</t>
         </is>
       </c>
     </row>
@@ -10243,11 +10243,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10270,76 +10270,6 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>US and UK Wholesale Price Indexes, 1790-1940</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>chapter</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>extenbook_published</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>phases_completed</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>["3_research", "4_adequacy", "5_ingestion", "6_extension", "7_replication", "8_output"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>artifacts</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>{"research_json": "Technical/research/S501_research.json", "adequacy_report": "Technical/docs/chapters/CH5_ADEQUACY_REPORT.json", "dpr": "Technical/docs/series/S501_DPR.md", "epr": "Technical/docs/series/S501_EPR.md", "loader": "Technical/code/L01_loaders/L01_S501_load.py", "processor": "Technical/code/P02_processors/P02_S501_construct.py", "validator": "Technical/code/V03_validators/V03_S501_validate.py", "processed": "Technical/data/processed/S501.parquet", "chopped_csv": "Technical/chopped/S501.csv", "extenbook_xlsx": "Technical/extenbooks/S501_extenbook.xlsx"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>updated_at</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-05-19T00:02:50.662623+00:00</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/extenbooks/S501_extenbook.xlsx
+++ b/extenbooks/S501_extenbook.xlsx
@@ -10228,7 +10228,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-05-19T00:03:28.841404+00:00</t>
+          <t>2026-07-02T06:24:27.990249+00:00</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S501_extenbook.xlsx
+++ b/extenbooks/S501_extenbook.xlsx
@@ -10228,7 +10228,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-02T06:24:27.990249+00:00</t>
+          <t>2026-07-11T03:44:24.982880+00:00</t>
         </is>
       </c>
     </row>
@@ -10243,11 +10243,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10270,6 +10270,162 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>primary_source</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SHAIKH_APPENDIX_5_DATALRPRICES</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>book_period_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>validation_class</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>pipeline_consistent</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>triage</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>{"verdict": "publish", "reason": "Faithful reconstruction of Shaikh Figure 5.3 (Ch5). Two clean country price-index lines on a single 1930=100 base, 1790-1940, read directly from Shaikh's Appendix 5 DATALRprices workbook. Single-unit, renders sensibly one trace per country; the chronological-slice parent of S502. Documents the absence of secular price trend before the 1939/40 fiat-money transition.", "date": "2026-06-10"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>dpr</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S501_DPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>epr</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S501_EPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Chronological slice of S502; enforce single-loader policy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>content_type</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>time_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>index_1930=100</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>proxy</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>chapter</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
